--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3959,8 +4081,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3975,923 +4101,985 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상사 천리몽 — 민요채보-2/상사 천리몽.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太
-―</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">상사 천리몽</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">太
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">잠</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 太</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">잠</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 潢</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" s="17"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" s="14"/>
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="17"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林
-―</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林
-―</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">林
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">林
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="17"/>
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="M5" s="17"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="C6" s="18"/>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K6" s="18"/>
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="M6" s="18"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 汰</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="16"/>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 汰</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">깨</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 南</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 林</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 潢</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">추</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="17"/>
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="20"/>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="G8" s="20"/>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑
 浹</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">빛</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="17"/>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 浹</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">浹
-―</t>
-        </is>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="G9" s="17"/>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">浹
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I9" s="20"/>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 浹</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="M9" s="17"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="18"/>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="E10" s="18"/>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="M10" s="18"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 浹</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="16"/>
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">말</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 浹</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 潢</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">선</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 潢</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C12" s="17"/>
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="20"/>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">浹</t>
         </is>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="G12" s="20"/>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-―</t>
-        </is>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">쓸</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 浹</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K13" s="17"/>
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="M13" s="17"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="18"/>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="18"/>
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="18"/>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="18"/>
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="M14" s="18"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" s="16"/>
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 太</t>
         </is>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" s="16"/>
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 林</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 潢</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">치</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">몸</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 浹</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="14"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 林</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="17"/>
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">浹</t>
         </is>
       </c>
-      <c r="I16" s="3"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" s="20"/>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="L16" s="14"/>
+      <c r="M16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="17"/>
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" s="17"/>
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G17" s="17"/>
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 林</t>
         </is>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="17"/>
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">림</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="M17" s="17"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="18"/>
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" s="18"/>
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G18" s="18"/>
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I18" s="18"/>
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="K18" s="18"/>
+      <c r="L18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M18" s="2"/>
+      <c r="M18" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I3" s="2"/>
@@ -659,12 +659,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -735,12 +735,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -885,13 +885,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -921,13 +921,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1036,13 +1036,13 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―|汰</t>
+          <t xml:space="preserve">無|–|汰</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 汰</t>
         </is>
       </c>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -1149,13 +1149,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林|―</t>
+          <t xml:space="preserve">林|–</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―</t>
+–</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|林|姑</t>
+          <t xml:space="preserve">–|林|姑</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 林
 姑</t>
         </is>
@@ -1457,13 +1457,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|―</t>
+          <t xml:space="preserve">淋|–</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1573,13 +1573,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林|―</t>
+          <t xml:space="preserve">林|–</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―</t>
+–</t>
         </is>
       </c>
       <c r="I29" s="2"/>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -1761,13 +1761,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -1912,13 +1912,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|林|姑</t>
+          <t xml:space="preserve">–|林|姑</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 林
 姑</t>
         </is>
@@ -2330,13 +2330,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林|―|○</t>
+          <t xml:space="preserve">林|–|○</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―
+–
 ○</t>
         </is>
       </c>
@@ -2367,13 +2367,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太|―</t>
+          <t xml:space="preserve">太|–</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-―</t>
+–</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2442,13 +2442,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林|―</t>
+          <t xml:space="preserve">林|–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―</t>
+–</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2557,13 +2557,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―</t>
+          <t xml:space="preserve">無|–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2744,13 +2744,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|林</t>
+          <t xml:space="preserve">–|林</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 林</t>
         </is>
       </c>
@@ -2935,12 +2935,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -2990,7 +2990,7 @@
       <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-―</t>
+–</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―</t>
+–</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -3065,7 +3065,7 @@
       <c r="B5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―</t>
+–</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -3112,13 +3112,13 @@
       <c r="C6" s="2"/>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 林
 姑</t>
         </is>
@@ -3126,7 +3126,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3148,7 +3148,7 @@
       <c r="D7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       <c r="B8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―</t>
+–</t>
         </is>
       </c>
       <c r="C8" s="2"/>
@@ -3205,7 +3205,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -3308,7 +3308,7 @@
       <c r="F11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="2"/>
@@ -3352,7 +3352,7 @@
       <c r="H12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -3362,7 +3362,7 @@
       <c r="B13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       <c r="C14" s="2"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 林
 姑</t>
         </is>
@@ -3423,7 +3423,7 @@
       <c r="F14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―</t>
+–</t>
         </is>
       </c>
       <c r="G14" s="2"/>
@@ -3485,7 +3485,7 @@
       <c r="A16" s="0"/>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 林</t>
         </is>
       </c>
@@ -3506,7 +3506,7 @@
       <c r="H16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―
+–
 汰</t>
         </is>
       </c>
@@ -3563,7 +3563,7 @@
       <c r="A18" s="0"/>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -3571,21 +3571,21 @@
       <c r="D18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―
+–
 ○</t>
         </is>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2972,61 +3001,61 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">상사 천리몽</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 –</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈아</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">잠못</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 –</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님을</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">춘하</t>
         </is>
@@ -3034,146 +3063,146 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="22"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="22"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="22"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 –</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈아</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">드네</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">그리며</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 林
 姑</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">깨길을</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">옥백을</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">추동</t>
         </is>
@@ -3181,148 +3210,148 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="22"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="22"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑
 仲</t>
         </is>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="24"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">말어라</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 林</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">헤미</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 林</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">안고</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 ○</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="22"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="22"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="22"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 ○</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님을쓸어</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 潢</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">산에노프아</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 –</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이밤</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사시</t>
         </is>
@@ -3330,75 +3359,75 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">안고</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">그리도</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 林</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">절에</t>
         </is>
@@ -3406,76 +3435,76 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="22"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 林
 姑</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="22"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 –</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="22"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 太</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">몸부림</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 林</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">못오시는</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 潢</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">상시라</t>
         </is>
@@ -3483,77 +3512,77 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 林</t>
         </is>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="22"/>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="22"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="22"/>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –
 汰</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">치네</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 太</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">개아</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 淋</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">청리</t>
         </is>
@@ -3561,35 +3590,35 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="22"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 –
 ○</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="22"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="22"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="I18" s="2"/>
+      <c r="I18" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -2986,20 +2986,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="I4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="I5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="I8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="I9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="I10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="I16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -653,12 +653,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -799,12 +799,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -834,13 +834,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚|○</t>
+          <t xml:space="preserve">○</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-○</t>
+          <t xml:space="preserve">○</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -3126,7 +3125,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I5" s="22"/>
@@ -3276,7 +3275,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -3304,8 +3303,7 @@
       <c r="G10" s="22"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚
-○</t>
+          <t xml:space="preserve">○</t>
         </is>
       </c>
       <c r="I10" s="22"/>

--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -834,12 +834,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -1141,13 +1141,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1753,13 +1752,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -2358,14 +2356,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林|–|○</t>
+          <t xml:space="preserve">林|–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–
-○</t>
+–</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2661,13 +2658,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林|○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -2963,13 +2959,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -3284,8 +3279,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C10" s="22"/>
@@ -3303,7 +3297,7 @@
       <c r="G10" s="22"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I10" s="22"/>
@@ -3590,30 +3584,26 @@
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–
-○</t>
+–</t>
         </is>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G18" s="22"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I18" s="22"/>

--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -3018,7 +3018,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈아</t>
+          <t xml:space="preserve">꿈
+아</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -3029,7 +3030,8 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">잠못</t>
+          <t xml:space="preserve">잠
+못</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -3040,7 +3042,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">님을</t>
+          <t xml:space="preserve">님
+을</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -3051,7 +3054,8 @@
       </c>
       <c r="I3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">춘하</t>
+          <t xml:space="preserve">춘
+하</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3097,8 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈아</t>
+          <t xml:space="preserve">꿈
+아</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -3104,7 +3109,8 @@
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">드네</t>
+          <t xml:space="preserve">드
+네</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -3115,7 +3121,9 @@
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">그리며</t>
+          <t xml:space="preserve">그
+리
+며</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -3165,7 +3173,9 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">깨길을</t>
+          <t xml:space="preserve">깨
+길
+을</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -3187,7 +3197,9 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">옥백을</t>
+          <t xml:space="preserve">옥
+백
+을</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -3198,7 +3210,8 @@
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">추동</t>
+          <t xml:space="preserve">추
+동</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3256,9 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">말어라</t>
+          <t xml:space="preserve">말
+어
+라</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -3254,7 +3269,8 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">헤미</t>
+          <t xml:space="preserve">헤
+미</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -3265,7 +3281,8 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">안고</t>
+          <t xml:space="preserve">안
+고</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -3312,7 +3329,10 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">님을쓸어</t>
+          <t xml:space="preserve">님
+을
+쓸
+어</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -3323,7 +3343,11 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">산에노프아</t>
+          <t xml:space="preserve">산
+에
+노
+프
+아</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -3334,7 +3358,8 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">이밤</t>
+          <t xml:space="preserve">이
+밤</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -3345,7 +3370,8 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">사시</t>
+          <t xml:space="preserve">사
+시</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3414,8 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">안고</t>
+          <t xml:space="preserve">안
+고</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -3399,7 +3426,9 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">그리도</t>
+          <t xml:space="preserve">그
+리
+도</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -3421,7 +3450,8 @@
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">절에</t>
+          <t xml:space="preserve">절
+에</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3495,9 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">몸부림</t>
+          <t xml:space="preserve">몸
+부
+림</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -3476,7 +3508,10 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">못오시는</t>
+          <t xml:space="preserve">못
+오
+시
+는</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -3498,7 +3533,9 @@
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">상시라</t>
+          <t xml:space="preserve">상
+시
+라</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3580,8 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">치네</t>
+          <t xml:space="preserve">치
+네</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -3554,7 +3592,8 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">개아</t>
+          <t xml:space="preserve">개
+아</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -3576,7 +3615,8 @@
       </c>
       <c r="I17" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">청리</t>
+          <t xml:space="preserve">청
+리</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -224,6 +229,12 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3016,7 +3027,7 @@
 –</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 아</t>
@@ -3028,7 +3039,7 @@
 –</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">잠
 못</t>
@@ -3040,7 +3051,7 @@
 –</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">님
 을</t>
@@ -3052,7 +3063,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">춘
 하</t>
@@ -3066,26 +3077,26 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C4" s="22"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E4" s="22"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="22"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I4" s="22"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
@@ -3095,7 +3106,7 @@
 –</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 아</t>
@@ -3107,7 +3118,7 @@
 無</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">드
 네</t>
@@ -3119,7 +3130,7 @@
 無</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 리
@@ -3131,7 +3142,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" s="22"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
@@ -3140,13 +3151,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
@@ -3154,14 +3165,14 @@
 姑</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
@@ -3171,7 +3182,7 @@
 汰</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">깨
 길
@@ -3184,7 +3195,7 @@
 –</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
@@ -3195,7 +3206,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">옥
 백
@@ -3208,7 +3219,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">추
 동</t>
@@ -3223,14 +3234,14 @@
 –</t>
         </is>
       </c>
-      <c r="C8" s="22"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="E8" s="22"/>
+      <c r="E8" s="25"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
@@ -3238,13 +3249,13 @@
 仲</t>
         </is>
       </c>
-      <c r="G8" s="24"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="22"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
@@ -3254,7 +3265,7 @@
 無</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">말
 어
@@ -3267,7 +3278,7 @@
 林</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">헤
 미</t>
@@ -3279,7 +3290,7 @@
 林</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">안
 고</t>
@@ -3290,7 +3301,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
@@ -3299,25 +3310,25 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C10" s="22"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="22"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G10" s="22"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" s="22"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
@@ -3327,7 +3338,7 @@
 汰</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">님
 을
@@ -3341,7 +3352,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">산
 에
@@ -3356,7 +3367,7 @@
 –</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 밤</t>
@@ -3368,7 +3379,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 시</t>
@@ -3382,27 +3393,27 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
@@ -3412,7 +3423,7 @@
 –</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">안
 고</t>
@@ -3424,7 +3435,7 @@
 無</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 리
@@ -3437,7 +3448,7 @@
 林</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3448,7 +3459,7 @@
 –</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">절
 에</t>
@@ -3462,7 +3473,7 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C14" s="22"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
@@ -3470,20 +3481,20 @@
 姑</t>
         </is>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 –</t>
         </is>
       </c>
-      <c r="G14" s="22"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I14" s="22"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
@@ -3493,7 +3504,7 @@
 太</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">몸
 부
@@ -3506,7 +3517,7 @@
 林</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 오
@@ -3520,7 +3531,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
@@ -3531,7 +3542,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">상
 시
@@ -3547,20 +3558,20 @@
 林</t>
         </is>
       </c>
-      <c r="C16" s="22"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E16" s="22"/>
+      <c r="E16" s="25"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G16" s="22"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -3568,7 +3579,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I16" s="22"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
@@ -3578,7 +3589,7 @@
 林</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">치
 네</t>
@@ -3590,7 +3601,7 @@
 太</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">개
 아</t>
@@ -3602,7 +3613,7 @@
 淋</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
@@ -3613,7 +3624,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">청
 리</t>
@@ -3627,26 +3638,26 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C18" s="22"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 –</t>
         </is>
       </c>
-      <c r="E18" s="22"/>
+      <c r="E18" s="25"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G18" s="22"/>
+      <c r="G18" s="25"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I18" s="22"/>
+      <c r="I18" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -695,10 +695,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -641,17 +641,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -768,7 +768,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -826,6 +826,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2292,234 +2336,234 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="54.79" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="I4" s="22"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="23" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="I6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="19" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="22" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B9" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="22" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="24" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2529,7 +2573,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="73"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/상사 천리몽.xlsx
+++ b/sheets/민요/검수/상사 천리몽.xlsx
@@ -2342,13 +2342,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
